--- a/Gestion/trésor.xlsx
+++ b/Gestion/trésor.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="153222"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11580"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27945" windowHeight="11580" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -13,24 +13,11 @@
     <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="204" count="204">
   <si>
     <t>niveau</t>
   </si>
@@ -309,177 +296,365 @@
   </si>
   <si>
     <t>x10</t>
+  </si>
+  <si>
+    <t>7d20x100pp</t>
+  </si>
+  <si>
+    <t>8d20x100pp</t>
+  </si>
+  <si>
+    <t>5-20/9</t>
+  </si>
+  <si>
+    <t>9d20x100pp</t>
+  </si>
+  <si>
+    <t>10d20x100pp</t>
+  </si>
+  <si>
+    <t>11d20x100pp</t>
+  </si>
+  <si>
+    <t>12d20x100pp</t>
+  </si>
+  <si>
+    <t>13d20x100pp</t>
+  </si>
+  <si>
+    <t>14d20x100pp</t>
+  </si>
+  <si>
+    <t>15d20x100pp</t>
+  </si>
+  <si>
+    <t>16d20x100pp</t>
+  </si>
+  <si>
+    <t>20/1~9</t>
+  </si>
+  <si>
+    <t>18/1~9</t>
+  </si>
+  <si>
+    <t>16/1~9</t>
+  </si>
+  <si>
+    <t>14/1~9</t>
+  </si>
+  <si>
+    <t>12/</t>
+  </si>
+  <si>
+    <t>18-20/1~9</t>
+  </si>
+  <si>
+    <t>20/1-9</t>
+  </si>
+  <si>
+    <t>18-20/1-9</t>
+  </si>
+  <si>
+    <t>16-20/1-9</t>
+  </si>
+  <si>
+    <t>14-20/1-9</t>
+  </si>
+  <si>
+    <t>12-20/1-9</t>
+  </si>
+  <si>
+    <t>10-20/1-9</t>
+  </si>
+  <si>
+    <t>8-20/1-9</t>
+  </si>
+  <si>
+    <t>5-20/10</t>
+  </si>
+  <si>
+    <t>5-20/11</t>
+  </si>
+  <si>
+    <t>5-20/12</t>
+  </si>
+  <si>
+    <t>6-20/1-9</t>
+  </si>
+  <si>
+    <t>4-20/1-9</t>
+  </si>
+  <si>
+    <t>2-20/1-9</t>
+  </si>
+  <si>
+    <t>1-9</t>
+  </si>
+  <si>
+    <t>1-10</t>
+  </si>
+  <si>
+    <t>1-11</t>
+  </si>
+  <si>
+    <t>1-12</t>
+  </si>
+  <si>
+    <t>1-13</t>
+  </si>
+  <si>
+    <t>1-14</t>
+  </si>
+  <si>
+    <t>1-15</t>
+  </si>
+  <si>
+    <t>1-16</t>
+  </si>
+  <si>
+    <t>1-17</t>
+  </si>
+  <si>
+    <t>1-18</t>
+  </si>
+  <si>
+    <t>1-19</t>
+  </si>
+  <si>
+    <t>1-20</t>
+  </si>
+  <si>
+    <t>1-21</t>
+  </si>
+  <si>
+    <t>1-22</t>
+  </si>
+  <si>
+    <t>1-23</t>
+  </si>
+  <si>
+    <t>1-24</t>
+  </si>
+  <si>
+    <t>1-25</t>
+  </si>
+  <si>
+    <t>1-26</t>
+  </si>
+  <si>
+    <t>1-27</t>
+  </si>
+  <si>
+    <t>1-28</t>
+  </si>
+  <si>
+    <t>17d20x100pp</t>
+  </si>
+  <si>
+    <t>18d20x100pp</t>
+  </si>
+  <si>
+    <t>19d20x100pp</t>
+  </si>
+  <si>
+    <t>20d20x100pp</t>
+  </si>
+  <si>
+    <t>21d20x100pp</t>
+  </si>
+  <si>
+    <t>21d20+10</t>
+  </si>
+  <si>
+    <t>(21d20+10)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+10)x101pp</t>
+  </si>
+  <si>
+    <t>(21d20+20)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+20)x101pp</t>
+  </si>
+  <si>
+    <t>(21d20+30)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+40)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+50)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+60)*100pp</t>
+  </si>
+  <si>
+    <t>(21d20+70)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+80)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+90)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+110)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+120)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+130)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+140)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+150)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+160)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+170)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+180)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+190)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+200)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+140)x101pp</t>
+  </si>
+  <si>
+    <t>(21d20+150)x101pp</t>
+  </si>
+  <si>
+    <t>(21d20+160)x101pp</t>
+  </si>
+  <si>
+    <t>(21d20+210)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+220)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+230)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+240)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+250)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+260)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+260)x101pp</t>
+  </si>
+  <si>
+    <t>(21d20+260)x102pp</t>
+  </si>
+  <si>
+    <t>(21d20+270)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+280)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+290)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+300)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+310)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+320)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+330)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+340)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+350)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+360)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+370)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+380)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+390)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+400)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+410)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+420)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+430)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+440)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+450)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+460)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+470)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+480)x100pp</t>
+  </si>
+  <si>
+    <t>(21d20+490)x100pp</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_-&quot;€&quot;* #,##0.00_-;\-&quot;€&quot;* #,##0.00_-;_-&quot;€&quot;* \-??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;€&quot;* #,##0_-;\-&quot;€&quot;* #,##0_-;_-&quot;€&quot;* \-_-;_-@_-"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="0" formatCode="General"/>
+    <numFmt numFmtId="49" formatCode="@"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="3">
     <font>
+      <name val="Arial"/>
       <sz val="11"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <charset val="134"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Arial"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -488,198 +663,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FF70AD46"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -687,337 +676,55 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="桁区切り" xfId="1" builtinId="3"/>
-    <cellStyle name="通貨" xfId="2" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="3" builtinId="5"/>
-    <cellStyle name="桁区切り[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="通貨[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="ハイパーリンク" xfId="6" builtinId="8"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="7" builtinId="9"/>
-    <cellStyle name="メモ" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文" xfId="9" builtinId="11"/>
-    <cellStyle name="タイトル" xfId="10" builtinId="15"/>
-    <cellStyle name="説明文" xfId="11" builtinId="53"/>
-    <cellStyle name="見出し 1" xfId="12" builtinId="16"/>
-    <cellStyle name="見出し 2" xfId="13" builtinId="17"/>
-    <cellStyle name="見出し 3" xfId="14" builtinId="18"/>
-    <cellStyle name="見出し 4" xfId="15" builtinId="19"/>
-    <cellStyle name="入力" xfId="16" builtinId="20"/>
-    <cellStyle name="出力" xfId="17" builtinId="21"/>
-    <cellStyle name="計算" xfId="18" builtinId="22"/>
-    <cellStyle name="チェックセル" xfId="19" builtinId="23"/>
-    <cellStyle name="リンクセル" xfId="20" builtinId="24"/>
-    <cellStyle name="集計" xfId="21" builtinId="25"/>
-    <cellStyle name="良い" xfId="22" builtinId="26"/>
-    <cellStyle name="悪い" xfId="23" builtinId="27"/>
-    <cellStyle name="どちらでもない" xfId="24" builtinId="28"/>
-    <cellStyle name="アクセント 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - アクセント 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - アクセント 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - アクセント 1" xfId="28" builtinId="32"/>
-    <cellStyle name="アクセント 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - アクセント 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - アクセント 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - アクセント 2" xfId="32" builtinId="36"/>
-    <cellStyle name="アクセント 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - アクセント 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - アクセント 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - アクセント 3" xfId="36" builtinId="40"/>
-    <cellStyle name="アクセント 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - アクセント 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - アクセント 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - アクセント 4" xfId="40" builtinId="44"/>
-    <cellStyle name="アクセント 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - アクセント 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - アクセント 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - アクセント 5" xfId="44" builtinId="48"/>
-    <cellStyle name="アクセント 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - アクセント 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - アクセント 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - アクセント 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <dxfs count="0"/>
+  <tableStyles defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16" count="0"/>
 </styleSheet>
 </file>
 
@@ -1273,26 +980,26 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:P101"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:AD111"/>
+  <sheetFormatPr defaultRowHeight="14.25" defaultColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="22.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="60.625" style="2" customWidth="1"/>
-    <col min="3" max="4" width="22.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="22.5" customWidth="1"/>
-    <col min="6" max="6" width="22.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22.5" customWidth="1"/>
-    <col min="8" max="9" width="22.5" style="1" customWidth="1"/>
-    <col min="10" max="16" width="22.375" style="1" customWidth="1"/>
+    <col min="1" max="1" customWidth="1" width="22.5" style="1"/>
+    <col min="2" max="2" customWidth="1" width="60.625" style="2"/>
+    <col min="3" max="4" customWidth="1" width="22.5" style="1"/>
+    <col min="5" max="5" customWidth="1" width="22.5" style="0"/>
+    <col min="6" max="6" customWidth="1" width="22.5" style="1"/>
+    <col min="7" max="7" customWidth="1" width="22.5" style="0"/>
+    <col min="8" max="9" customWidth="1" width="22.5" style="1"/>
+    <col min="10" max="16" customWidth="1" width="22.375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1" spans="1:16">
+    <row r="1" spans="8:8" ht="13.5" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1342,9 +1049,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="8:8">
       <c r="A2" s="4">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>16</v>
@@ -1359,7 +1066,7 @@
         <v>17</v>
       </c>
       <c r="J2" s="4">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
@@ -1368,9 +1075,9 @@
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="8:8">
       <c r="A3" s="4">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>18</v>
@@ -1387,7 +1094,7 @@
         <v>20</v>
       </c>
       <c r="J3" s="4">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
@@ -1396,9 +1103,9 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="8:8">
       <c r="A4" s="4">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>21</v>
@@ -1415,7 +1122,7 @@
         <v>23</v>
       </c>
       <c r="J4" s="4">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
@@ -1424,9 +1131,9 @@
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="8:8">
       <c r="A5" s="4">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>24</v>
@@ -1443,7 +1150,7 @@
         <v>26</v>
       </c>
       <c r="J5" s="4">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -1452,9 +1159,9 @@
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="8:8">
       <c r="A6" s="4">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>27</v>
@@ -1471,7 +1178,7 @@
         <v>29</v>
       </c>
       <c r="J6" s="4">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -1480,9 +1187,9 @@
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="8:8" ht="14.9">
       <c r="A7" s="4">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>30</v>
@@ -1501,7 +1208,7 @@
         <v>32</v>
       </c>
       <c r="J7" s="4">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -1510,9 +1217,9 @@
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="8:8" ht="14.9">
       <c r="A8" s="4">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>33</v>
@@ -1531,7 +1238,7 @@
         <v>35</v>
       </c>
       <c r="J8" s="4">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -1540,9 +1247,9 @@
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="8:8" ht="14.9">
       <c r="A9" s="4">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>36</v>
@@ -1561,7 +1268,7 @@
         <v>38</v>
       </c>
       <c r="J9" s="4">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -1570,9 +1277,9 @@
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="8:8" ht="14.9">
       <c r="A10" s="4">
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>39</v>
@@ -1591,7 +1298,7 @@
         <v>41</v>
       </c>
       <c r="J10" s="4">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -1600,9 +1307,9 @@
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="8:8" ht="14.9">
       <c r="A11" s="4">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>42</v>
@@ -1623,7 +1330,7 @@
         <v>44</v>
       </c>
       <c r="J11" s="4">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -1632,9 +1339,9 @@
       <c r="O11" s="4"/>
       <c r="P11" s="4"/>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="8:8" ht="14.9">
       <c r="A12" s="4">
-        <v>11</v>
+        <v>11.0</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>45</v>
@@ -1655,7 +1362,7 @@
         <v>44</v>
       </c>
       <c r="J12" s="4">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1664,9 +1371,9 @@
       <c r="O12" s="4"/>
       <c r="P12" s="4"/>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="8:8" ht="14.9">
       <c r="A13" s="4">
-        <v>12</v>
+        <v>12.0</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>47</v>
@@ -1687,7 +1394,7 @@
         <v>44</v>
       </c>
       <c r="J13" s="4">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1696,9 +1403,9 @@
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="8:8" ht="14.9">
       <c r="A14" s="4">
-        <v>13</v>
+        <v>13.0</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>49</v>
@@ -1719,7 +1426,7 @@
         <v>44</v>
       </c>
       <c r="J14" s="4">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1728,9 +1435,9 @@
       <c r="O14" s="4"/>
       <c r="P14" s="4"/>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="8:8" ht="14.9">
       <c r="A15" s="4">
-        <v>14</v>
+        <v>14.0</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>51</v>
@@ -1753,7 +1460,7 @@
         <v>44</v>
       </c>
       <c r="J15" s="4">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1762,9 +1469,9 @@
       <c r="O15" s="4"/>
       <c r="P15" s="4"/>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="8:8" ht="14.9">
       <c r="A16" s="4">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>53</v>
@@ -1787,7 +1494,7 @@
         <v>44</v>
       </c>
       <c r="J16" s="4">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1796,9 +1503,9 @@
       <c r="O16" s="4"/>
       <c r="P16" s="4"/>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="8:8" ht="14.9">
       <c r="A17" s="4">
-        <v>16</v>
+        <v>16.0</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>55</v>
@@ -1821,7 +1528,7 @@
         <v>44</v>
       </c>
       <c r="J17" s="4">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1830,9 +1537,9 @@
       <c r="O17" s="4"/>
       <c r="P17" s="4"/>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="8:8" ht="14.9">
       <c r="A18" s="4">
-        <v>17</v>
+        <v>17.0</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>57</v>
@@ -1855,7 +1562,7 @@
         <v>44</v>
       </c>
       <c r="J18" s="4">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1864,9 +1571,9 @@
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="8:8" ht="14.9">
       <c r="A19" s="4">
-        <v>18</v>
+        <v>18.0</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>59</v>
@@ -1891,7 +1598,7 @@
         <v>44</v>
       </c>
       <c r="J19" s="4">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1900,9 +1607,9 @@
       <c r="O19" s="4"/>
       <c r="P19" s="4"/>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="8:8" ht="14.9">
       <c r="A20" s="4">
-        <v>19</v>
+        <v>19.0</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>61</v>
@@ -1927,7 +1634,7 @@
         <v>44</v>
       </c>
       <c r="J20" s="4">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1936,9 +1643,9 @@
       <c r="O20" s="4"/>
       <c r="P20" s="4"/>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="8:8" ht="14.9">
       <c r="A21" s="4">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>62</v>
@@ -1963,7 +1670,7 @@
         <v>64</v>
       </c>
       <c r="J21" s="4">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1972,9 +1679,9 @@
       <c r="O21" s="4"/>
       <c r="P21" s="4"/>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="8:8" ht="14.9">
       <c r="A22" s="4">
-        <v>21</v>
+        <v>21.0</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>65</v>
@@ -1999,7 +1706,7 @@
         <v>64</v>
       </c>
       <c r="J22" s="4">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -2008,9 +1715,9 @@
       <c r="O22" s="4"/>
       <c r="P22" s="4"/>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="8:8" ht="14.9">
       <c r="A23" s="4">
-        <v>22</v>
+        <v>22.0</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>66</v>
@@ -2037,7 +1744,7 @@
         <v>64</v>
       </c>
       <c r="J23" s="4">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -2046,9 +1753,9 @@
       <c r="O23" s="4"/>
       <c r="P23" s="4"/>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="8:8" ht="14.9">
       <c r="A24" s="4">
-        <v>23</v>
+        <v>23.0</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>67</v>
@@ -2075,7 +1782,7 @@
         <v>64</v>
       </c>
       <c r="J24" s="4">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -2084,9 +1791,9 @@
       <c r="O24" s="4"/>
       <c r="P24" s="4"/>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="8:8" ht="14.9">
       <c r="A25" s="4">
-        <v>24</v>
+        <v>24.0</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>69</v>
@@ -2113,7 +1820,7 @@
         <v>64</v>
       </c>
       <c r="J25" s="4">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -2122,9 +1829,9 @@
       <c r="O25" s="4"/>
       <c r="P25" s="4"/>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="8:8" ht="14.9">
       <c r="A26" s="4">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>70</v>
@@ -2151,7 +1858,7 @@
         <v>64</v>
       </c>
       <c r="J26" s="4">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -2160,9 +1867,9 @@
       <c r="O26" s="4"/>
       <c r="P26" s="4"/>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="8:8" ht="14.9">
       <c r="A27" s="4">
-        <v>26</v>
+        <v>26.0</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>71</v>
@@ -2189,7 +1896,7 @@
         <v>64</v>
       </c>
       <c r="J27" s="4">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -2198,9 +1905,9 @@
       <c r="O27" s="4"/>
       <c r="P27" s="4"/>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="8:8" ht="14.9">
       <c r="A28" s="4">
-        <v>27</v>
+        <v>27.0</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>72</v>
@@ -2227,7 +1934,7 @@
         <v>64</v>
       </c>
       <c r="J28" s="4">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -2236,9 +1943,9 @@
       <c r="O28" s="4"/>
       <c r="P28" s="4"/>
     </row>
-    <row r="29" spans="1:16">
+    <row r="29" spans="8:8" ht="14.9">
       <c r="A29" s="4">
-        <v>28</v>
+        <v>28.0</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>73</v>
@@ -2265,7 +1972,7 @@
         <v>64</v>
       </c>
       <c r="J29" s="4">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -2274,9 +1981,9 @@
       <c r="O29" s="4"/>
       <c r="P29" s="4"/>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="8:8" ht="14.9">
       <c r="A30" s="4">
-        <v>29</v>
+        <v>29.0</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>75</v>
@@ -2303,7 +2010,7 @@
         <v>64</v>
       </c>
       <c r="J30" s="4">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -2312,9 +2019,9 @@
       <c r="O30" s="4"/>
       <c r="P30" s="4"/>
     </row>
-    <row r="31" spans="1:16">
+    <row r="31" spans="8:8" ht="14.9">
       <c r="A31" s="4">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>76</v>
@@ -2341,7 +2048,7 @@
         <v>77</v>
       </c>
       <c r="J31" s="4">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -2350,9 +2057,9 @@
       <c r="O31" s="4"/>
       <c r="P31" s="4"/>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="8:8" ht="14.9">
       <c r="A32" s="4">
-        <v>31</v>
+        <v>31.0</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>78</v>
@@ -2379,7 +2086,7 @@
         <v>77</v>
       </c>
       <c r="J32" s="4">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -2388,9 +2095,9 @@
       <c r="O32" s="4"/>
       <c r="P32" s="4"/>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="8:8" ht="14.9">
       <c r="A33" s="4">
-        <v>32</v>
+        <v>32.0</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>79</v>
@@ -2417,7 +2124,7 @@
         <v>77</v>
       </c>
       <c r="J33" s="4">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -2426,9 +2133,9 @@
       <c r="O33" s="4"/>
       <c r="P33" s="4"/>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="8:8" ht="14.9">
       <c r="A34" s="4">
-        <v>33</v>
+        <v>33.0</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>80</v>
@@ -2455,7 +2162,7 @@
         <v>77</v>
       </c>
       <c r="J34" s="4">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -2464,9 +2171,9 @@
       <c r="O34" s="4"/>
       <c r="P34" s="4"/>
     </row>
-    <row r="35" spans="1:16">
+    <row r="35" spans="8:8" ht="14.9">
       <c r="A35" s="4">
-        <v>34</v>
+        <v>34.0</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>81</v>
@@ -2493,7 +2200,7 @@
         <v>77</v>
       </c>
       <c r="J35" s="4">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -2502,9 +2209,9 @@
       <c r="O35" s="4"/>
       <c r="P35" s="4"/>
     </row>
-    <row r="36" spans="1:16">
+    <row r="36" spans="8:8" ht="14.9">
       <c r="A36" s="4">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>82</v>
@@ -2531,7 +2238,7 @@
         <v>77</v>
       </c>
       <c r="J36" s="4">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -2540,9 +2247,9 @@
       <c r="O36" s="4"/>
       <c r="P36" s="4"/>
     </row>
-    <row r="37" spans="1:16">
+    <row r="37" spans="8:8" ht="14.9">
       <c r="A37" s="4">
-        <v>36</v>
+        <v>36.0</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>84</v>
@@ -2569,7 +2276,7 @@
         <v>77</v>
       </c>
       <c r="J37" s="4">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -2578,9 +2285,9 @@
       <c r="O37" s="4"/>
       <c r="P37" s="4"/>
     </row>
-    <row r="38" spans="1:16">
+    <row r="38" spans="8:8" ht="14.9">
       <c r="A38" s="4">
-        <v>37</v>
+        <v>37.0</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>85</v>
@@ -2607,7 +2314,7 @@
         <v>77</v>
       </c>
       <c r="J38" s="4">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -2616,22 +2323,36 @@
       <c r="O38" s="4"/>
       <c r="P38" s="4"/>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="8:8" ht="14.9">
       <c r="A39" s="4">
-        <v>38</v>
-      </c>
-      <c r="B39" s="7"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
+        <v>38.0</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="I39" s="7" t="s">
         <v>77</v>
       </c>
       <c r="J39" s="4">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -2640,22 +2361,36 @@
       <c r="O39" s="4"/>
       <c r="P39" s="4"/>
     </row>
-    <row r="40" spans="1:16">
+    <row r="40" spans="8:8" ht="14.9">
       <c r="A40" s="4">
-        <v>39</v>
-      </c>
-      <c r="B40" s="7"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
+        <v>39.0</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="I40" s="7" t="s">
         <v>77</v>
       </c>
       <c r="J40" s="4">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -2664,816 +2399,2751 @@
       <c r="O40" s="4"/>
       <c r="P40" s="4"/>
     </row>
-    <row r="41" spans="1:16">
+    <row r="41" spans="8:8" ht="14.9">
       <c r="A41" s="4">
-        <v>40</v>
-      </c>
-      <c r="B41" s="7"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
+        <v>40.0</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>63</v>
+      </c>
       <c r="I41" s="7" t="s">
         <v>86</v>
       </c>
       <c r="J41" s="4">
-        <v>8</v>
-      </c>
-      <c r="K41" s="4"/>
+        <v>8.0</v>
+      </c>
+      <c r="K41" s="6"/>
       <c r="L41" s="4"/>
       <c r="M41" s="4"/>
       <c r="N41" s="4"/>
       <c r="O41" s="4"/>
       <c r="P41" s="4"/>
     </row>
-    <row r="42" spans="1:16">
+    <row r="42" spans="8:8" ht="14.9">
       <c r="A42" s="4">
-        <v>41</v>
-      </c>
-      <c r="B42" s="7"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
+        <v>41.0</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>63</v>
+      </c>
       <c r="I42" s="7" t="s">
         <v>86</v>
       </c>
       <c r="J42" s="4">
-        <v>9</v>
-      </c>
-      <c r="K42" s="4"/>
+        <v>9.0</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>110</v>
+      </c>
       <c r="L42" s="4"/>
       <c r="M42" s="4"/>
       <c r="N42" s="4"/>
       <c r="O42" s="4"/>
       <c r="P42" s="4"/>
     </row>
-    <row r="43" spans="1:16">
+    <row r="43" spans="8:8" ht="14.9">
       <c r="A43" s="4">
-        <v>42</v>
-      </c>
-      <c r="B43" s="7"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="4"/>
+        <v>42.0</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>63</v>
+      </c>
       <c r="I43" s="7" t="s">
         <v>86</v>
       </c>
       <c r="J43" s="4">
-        <v>9</v>
-      </c>
-      <c r="K43" s="4"/>
+        <v>9.0</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>111</v>
+      </c>
       <c r="L43" s="4"/>
       <c r="M43" s="4"/>
       <c r="N43" s="4"/>
       <c r="O43" s="4"/>
       <c r="P43" s="4"/>
     </row>
-    <row r="44" spans="1:16">
+    <row r="44" spans="8:8" ht="14.9">
       <c r="A44" s="4">
-        <v>43</v>
-      </c>
-      <c r="B44" s="7"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="4"/>
+        <v>43.0</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>68</v>
+      </c>
       <c r="I44" s="7" t="s">
         <v>86</v>
       </c>
       <c r="J44" s="4">
-        <v>9</v>
-      </c>
-      <c r="K44" s="4"/>
+        <v>9.0</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>112</v>
+      </c>
       <c r="L44" s="4"/>
       <c r="M44" s="4"/>
       <c r="N44" s="4"/>
       <c r="O44" s="4"/>
       <c r="P44" s="4"/>
     </row>
-    <row r="45" spans="1:16">
+    <row r="45" spans="8:8" ht="14.9">
       <c r="A45" s="4">
-        <v>44</v>
-      </c>
-      <c r="B45" s="7"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="4"/>
+        <v>44.0</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>68</v>
+      </c>
       <c r="I45" s="7" t="s">
         <v>86</v>
       </c>
       <c r="J45" s="4">
-        <v>9</v>
-      </c>
-      <c r="K45" s="4"/>
+        <v>9.0</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>113</v>
+      </c>
       <c r="L45" s="4"/>
       <c r="M45" s="4"/>
       <c r="N45" s="4"/>
       <c r="O45" s="4"/>
       <c r="P45" s="4"/>
     </row>
-    <row r="46" spans="1:16">
+    <row r="46" spans="8:8" ht="14.9">
       <c r="A46" s="4">
-        <v>45</v>
-      </c>
-      <c r="B46" s="7"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="5"/>
-      <c r="H46" s="4"/>
+        <v>45.0</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>68</v>
+      </c>
       <c r="I46" s="7" t="s">
         <v>86</v>
       </c>
       <c r="J46" s="4">
-        <v>9</v>
-      </c>
-      <c r="K46" s="4"/>
+        <v>9.0</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>114</v>
+      </c>
       <c r="L46" s="4"/>
       <c r="M46" s="4"/>
       <c r="N46" s="4"/>
       <c r="O46" s="4"/>
       <c r="P46" s="4"/>
     </row>
-    <row r="47" spans="1:16">
+    <row r="47" spans="8:8" ht="14.9">
       <c r="A47" s="4">
-        <v>46</v>
-      </c>
-      <c r="B47" s="7"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="5"/>
-      <c r="H47" s="4"/>
+        <v>46.0</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>68</v>
+      </c>
       <c r="I47" s="7" t="s">
         <v>86</v>
       </c>
       <c r="J47" s="4">
-        <v>10</v>
-      </c>
-      <c r="K47" s="4"/>
+        <v>10.0</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>115</v>
+      </c>
       <c r="L47" s="4"/>
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
       <c r="O47" s="4"/>
       <c r="P47" s="4"/>
     </row>
-    <row r="48" spans="1:16">
+    <row r="48" spans="8:8" ht="14.9">
       <c r="A48" s="4">
-        <v>47</v>
-      </c>
-      <c r="B48" s="7"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="5"/>
-      <c r="H48" s="4"/>
+        <v>47.0</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>68</v>
+      </c>
       <c r="I48" s="7" t="s">
         <v>86</v>
       </c>
       <c r="J48" s="4">
-        <v>10</v>
-      </c>
-      <c r="K48" s="4"/>
+        <v>10.0</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>116</v>
+      </c>
       <c r="L48" s="4"/>
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
       <c r="O48" s="4"/>
       <c r="P48" s="4"/>
     </row>
-    <row r="49" spans="1:10">
-      <c r="A49" s="1">
-        <v>48</v>
-      </c>
-      <c r="I49" s="2" t="s">
+    <row r="49" spans="8:8" s="8" ht="14.9" customFormat="1">
+      <c r="A49" s="9">
+        <v>48.0</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I49" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="J49" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10">
-      <c r="A50" s="1">
-        <v>49</v>
-      </c>
-      <c r="I50" s="2" t="s">
+      <c r="J49" s="9">
+        <v>10.0</v>
+      </c>
+      <c r="K49" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="L49" s="9"/>
+      <c r="M49" s="9"/>
+      <c r="N49" s="9"/>
+      <c r="O49" s="9"/>
+      <c r="P49" s="9"/>
+    </row>
+    <row r="50" spans="8:8" s="8" ht="14.9" customFormat="1">
+      <c r="A50" s="9">
+        <v>49.0</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I50" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="J50" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10">
-      <c r="A51" s="1">
-        <v>50</v>
-      </c>
-      <c r="I51" s="2" t="s">
+      <c r="J50" s="9">
+        <v>10.0</v>
+      </c>
+      <c r="K50" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="L50" s="9"/>
+      <c r="M50" s="9"/>
+      <c r="N50" s="9"/>
+      <c r="O50" s="9"/>
+      <c r="P50" s="9"/>
+    </row>
+    <row r="51" spans="8:8" s="8" ht="14.9" customFormat="1">
+      <c r="A51" s="9">
+        <v>50.0</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H51" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I51" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="J51" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10">
-      <c r="A52" s="1">
-        <v>51</v>
-      </c>
-      <c r="I52" s="2" t="s">
+      <c r="J51" s="9">
+        <v>10.0</v>
+      </c>
+      <c r="K51" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="L51" s="9"/>
+      <c r="M51" s="9"/>
+      <c r="N51" s="9"/>
+      <c r="O51" s="9"/>
+      <c r="P51" s="9"/>
+    </row>
+    <row r="52" spans="8:8" s="8" ht="14.9" customFormat="1">
+      <c r="A52" s="9">
+        <v>51.0</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I52" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="J52" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10">
-      <c r="A53" s="1">
-        <v>52</v>
-      </c>
-      <c r="I53" s="2" t="s">
+      <c r="J52" s="9">
+        <v>11.0</v>
+      </c>
+      <c r="K52" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L52" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="M52" s="9"/>
+      <c r="N52" s="9"/>
+      <c r="O52" s="9"/>
+      <c r="P52" s="9"/>
+    </row>
+    <row r="53" spans="8:8" s="8" ht="14.9" customFormat="1">
+      <c r="A53" s="9">
+        <v>52.0</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G53" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H53" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I53" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="J53" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10">
-      <c r="A54" s="1">
-        <v>53</v>
-      </c>
-      <c r="I54" s="2" t="s">
+      <c r="J53" s="9">
+        <v>11.0</v>
+      </c>
+      <c r="K53" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L53" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="M53" s="9"/>
+      <c r="N53" s="9"/>
+      <c r="O53" s="9"/>
+      <c r="P53" s="9"/>
+    </row>
+    <row r="54" spans="8:8" s="8" ht="14.9" customFormat="1">
+      <c r="A54" s="9">
+        <v>53.0</v>
+      </c>
+      <c r="B54" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E54" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H54" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I54" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="J54" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10">
-      <c r="A55" s="1">
-        <v>54</v>
-      </c>
-      <c r="I55" s="2" t="s">
+      <c r="J54" s="9">
+        <v>11.0</v>
+      </c>
+      <c r="K54" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L54" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="M54" s="9"/>
+      <c r="N54" s="9"/>
+      <c r="O54" s="9"/>
+      <c r="P54" s="9"/>
+    </row>
+    <row r="55" spans="8:8" s="8" ht="14.9" customFormat="1">
+      <c r="A55" s="9">
+        <v>54.0</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G55" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I55" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="J55" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10">
-      <c r="A56" s="1">
-        <v>55</v>
-      </c>
-      <c r="I56" s="2" t="s">
+      <c r="J55" s="9">
+        <v>11.0</v>
+      </c>
+      <c r="K55" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L55" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="M55" s="9"/>
+      <c r="N55" s="9"/>
+      <c r="O55" s="9"/>
+      <c r="P55" s="9"/>
+    </row>
+    <row r="56" spans="8:8" s="8" ht="14.9" customFormat="1">
+      <c r="A56" s="9">
+        <v>55.0</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E56" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G56" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="I56" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="J56" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10">
-      <c r="A57" s="1">
-        <v>56</v>
-      </c>
-      <c r="I57" s="2" t="s">
+      <c r="J56" s="9">
+        <v>11.0</v>
+      </c>
+      <c r="K56" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L56" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="M56" s="9"/>
+      <c r="N56" s="9"/>
+      <c r="O56" s="9"/>
+      <c r="P56" s="9"/>
+    </row>
+    <row r="57" spans="8:8" s="8" ht="14.9" customFormat="1">
+      <c r="A57" s="9">
+        <v>56.0</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="I57" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="J57" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10">
-      <c r="A58" s="1">
-        <v>57</v>
-      </c>
-      <c r="I58" s="2" t="s">
+      <c r="J57" s="9">
+        <v>12.0</v>
+      </c>
+      <c r="K57" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L57" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="M57" s="9"/>
+      <c r="N57" s="9"/>
+      <c r="O57" s="9"/>
+      <c r="P57" s="9"/>
+    </row>
+    <row r="58" spans="8:8" s="8" ht="14.9" customFormat="1">
+      <c r="A58" s="9">
+        <v>57.0</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E58" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G58" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="I58" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="J58" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10">
-      <c r="A59" s="1">
-        <v>58</v>
-      </c>
-      <c r="I59" s="2" t="s">
+      <c r="J58" s="9">
+        <v>12.0</v>
+      </c>
+      <c r="K58" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L58" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="M58" s="9"/>
+      <c r="N58" s="9"/>
+      <c r="O58" s="9"/>
+      <c r="P58" s="9"/>
+    </row>
+    <row r="59" spans="8:8" s="8" ht="14.9" customFormat="1">
+      <c r="A59" s="9">
+        <v>58.0</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E59" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="G59" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H59" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="I59" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="J59" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10">
-      <c r="A60" s="1">
-        <v>59</v>
-      </c>
-      <c r="I60" s="2" t="s">
+      <c r="J59" s="9">
+        <v>12.0</v>
+      </c>
+      <c r="K59" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L59" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="M59" s="9"/>
+      <c r="N59" s="9"/>
+      <c r="O59" s="9"/>
+      <c r="P59" s="9"/>
+    </row>
+    <row r="60" spans="8:8" s="8" ht="14.9" customFormat="1">
+      <c r="A60" s="9">
+        <v>59.0</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="G60" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H60" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="I60" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="J60" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10">
-      <c r="A61" s="1">
-        <v>60</v>
-      </c>
-      <c r="I61" s="2" t="s">
+      <c r="J60" s="9">
+        <v>12.0</v>
+      </c>
+      <c r="K60" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L60" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="M60" s="9"/>
+      <c r="N60" s="9"/>
+      <c r="O60" s="9"/>
+      <c r="P60" s="9"/>
+    </row>
+    <row r="61" spans="8:8" s="8" ht="14.9" customFormat="1">
+      <c r="A61" s="9">
+        <v>60.0</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="G61" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H61" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="I61" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="J61" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10">
-      <c r="A62" s="1">
-        <v>61</v>
-      </c>
-      <c r="I62" s="2" t="s">
+      <c r="J61" s="9">
+        <v>12.0</v>
+      </c>
+      <c r="K61" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L61" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="M61" s="9"/>
+      <c r="N61" s="9"/>
+      <c r="O61" s="9"/>
+      <c r="P61" s="9"/>
+    </row>
+    <row r="62" spans="8:8" s="8" ht="14.9" customFormat="1">
+      <c r="A62" s="9">
+        <v>61.0</v>
+      </c>
+      <c r="B62" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="G62" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H62" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="I62" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="J62" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10">
-      <c r="A63" s="1">
-        <v>62</v>
-      </c>
-      <c r="I63" s="2" t="s">
+      <c r="J62" s="9">
+        <v>13.0</v>
+      </c>
+      <c r="K62" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L62" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M62" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="N62" s="9"/>
+      <c r="O62" s="9"/>
+      <c r="P62" s="9"/>
+    </row>
+    <row r="63" spans="8:8" s="8" ht="14.9" customFormat="1">
+      <c r="A63" s="9">
+        <v>62.0</v>
+      </c>
+      <c r="B63" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E63" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H63" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="I63" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="J63" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10">
-      <c r="A64" s="1">
-        <v>63</v>
-      </c>
-      <c r="I64" s="2" t="s">
+      <c r="J63" s="9">
+        <v>13.0</v>
+      </c>
+      <c r="K63" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L63" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M63" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="N63" s="9"/>
+      <c r="O63" s="9"/>
+      <c r="P63" s="9"/>
+    </row>
+    <row r="64" spans="8:8" s="8" ht="14.9" customFormat="1">
+      <c r="A64" s="9">
+        <v>63.0</v>
+      </c>
+      <c r="B64" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E64" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="G64" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H64" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="I64" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="J64" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10">
+      <c r="J64" s="9">
+        <v>13.0</v>
+      </c>
+      <c r="K64" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L64" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M64" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="N64" s="9"/>
+      <c r="O64" s="9"/>
+      <c r="P64" s="9"/>
+    </row>
+    <row r="65" spans="8:8" ht="14.9">
       <c r="A65" s="1">
-        <v>64</v>
+        <v>64.0</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>83</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>88</v>
       </c>
       <c r="J65" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10">
+        <v>13.0</v>
+      </c>
+      <c r="K65" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L65" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M65" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="66" spans="8:8" ht="14.9">
       <c r="A66" s="1">
-        <v>65</v>
+        <v>65.0</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E66" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="G66" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H66" s="9" t="s">
+        <v>83</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>88</v>
       </c>
       <c r="J66" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10">
+        <v>13.0</v>
+      </c>
+      <c r="K66" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L66" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M66" s="9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="67" spans="8:8" ht="14.9">
       <c r="A67" s="1">
-        <v>66</v>
+        <v>66.0</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E67" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>95</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>88</v>
       </c>
       <c r="J67" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10">
+        <v>14.0</v>
+      </c>
+      <c r="K67" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L67" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M67" s="9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="68" spans="8:8" ht="14.9">
       <c r="A68" s="1">
-        <v>67</v>
+        <v>67.0</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E68" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="G68" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H68" s="9" t="s">
+        <v>95</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>88</v>
       </c>
       <c r="J68" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10">
+        <v>14.0</v>
+      </c>
+      <c r="K68" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L68" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M68" s="9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="69" spans="8:8" ht="14.9">
       <c r="A69" s="1">
-        <v>68</v>
+        <v>68.0</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E69" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="G69" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>95</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>88</v>
       </c>
       <c r="J69" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10">
+        <v>14.0</v>
+      </c>
+      <c r="K69" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L69" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M69" s="9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="70" spans="8:8" ht="14.9">
       <c r="A70" s="1">
-        <v>69</v>
+        <v>69.0</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E70" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="F70" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="G70" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H70" s="9" t="s">
+        <v>95</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>88</v>
       </c>
       <c r="J70" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10">
+        <v>14.0</v>
+      </c>
+      <c r="K70" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L70" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M70" s="9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="71" spans="8:8" ht="14.9">
       <c r="A71" s="1">
-        <v>70</v>
+        <v>70.0</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E71" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="G71" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H71" s="9" t="s">
+        <v>95</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>89</v>
       </c>
       <c r="J71" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10">
+        <v>14.0</v>
+      </c>
+      <c r="K71" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L71" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M71" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="72" spans="8:8" ht="14.9">
       <c r="A72" s="1">
-        <v>71</v>
+        <v>71.0</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E72" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="F72" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="G72" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H72" s="9" t="s">
+        <v>95</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>89</v>
       </c>
       <c r="J72" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10">
+        <v>15.0</v>
+      </c>
+      <c r="K72" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L72" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M72" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N72" s="11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="73" spans="8:8" ht="14.9">
       <c r="A73" s="1">
-        <v>72</v>
+        <v>72.0</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D73" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E73" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>95</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>89</v>
       </c>
       <c r="J73" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10">
+        <v>15.0</v>
+      </c>
+      <c r="K73" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L73" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M73" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N73" s="9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="74" spans="8:8" ht="14.9">
       <c r="A74" s="1">
-        <v>73</v>
+        <v>73.0</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E74" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="F74" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="G74" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H74" s="9" t="s">
+        <v>95</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>89</v>
       </c>
       <c r="J74" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10">
+        <v>15.0</v>
+      </c>
+      <c r="K74" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L74" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M74" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N74" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="75" spans="8:8" ht="14.9">
       <c r="A75" s="1">
-        <v>74</v>
+        <v>74.0</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E75" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="G75" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="H75" s="9" t="s">
+        <v>95</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>89</v>
       </c>
       <c r="J75" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10">
+        <v>15.0</v>
+      </c>
+      <c r="K75" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L75" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M75" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N75" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="76" spans="8:8" ht="14.9">
       <c r="A76" s="1">
-        <v>75</v>
+        <v>75.0</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E76" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="F76" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="G76" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="H76" s="9" t="s">
+        <v>95</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>89</v>
       </c>
       <c r="J76" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10">
+        <v>15.0</v>
+      </c>
+      <c r="K76" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L76" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M76" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N76" s="9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="77" spans="8:8" ht="14.9">
       <c r="A77" s="1">
-        <v>76</v>
+        <v>76.0</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="G77" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="H77" s="9" t="s">
+        <v>95</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>89</v>
       </c>
       <c r="J77" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10">
+        <v>16.0</v>
+      </c>
+      <c r="K77" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L77" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M77" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N77" s="9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="78" spans="8:8" ht="14.9">
       <c r="A78" s="1">
-        <v>77</v>
+        <v>77.0</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="G78" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="H78" s="9" t="s">
+        <v>95</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>89</v>
       </c>
       <c r="J78" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10">
+        <v>16.0</v>
+      </c>
+      <c r="K78" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L78" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M78" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N78" s="9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="79" spans="8:8" ht="14.9">
       <c r="A79" s="1">
-        <v>78</v>
+        <v>78.0</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="G79" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>117</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>89</v>
       </c>
       <c r="J79" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10">
+        <v>16.0</v>
+      </c>
+      <c r="K79" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L79" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M79" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N79" s="9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="80" spans="8:8" ht="14.9">
       <c r="A80" s="1">
-        <v>79</v>
+        <v>79.0</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="G80" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="H80" s="9" t="s">
+        <v>117</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>89</v>
       </c>
       <c r="J80" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10">
+        <v>16.0</v>
+      </c>
+      <c r="K80" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L80" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M80" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N80" s="9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="81" spans="8:8" ht="14.9">
       <c r="A81" s="1">
-        <v>80</v>
+        <v>80.0</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G81" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="H81" s="9" t="s">
+        <v>117</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>90</v>
       </c>
       <c r="J81" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10">
+        <v>16.0</v>
+      </c>
+      <c r="K81" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L81" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M81" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N81" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="82" spans="8:8" ht="14.9">
       <c r="A82" s="1">
-        <v>81</v>
+        <v>81.0</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G82" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="H82" s="9" t="s">
+        <v>117</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>90</v>
       </c>
       <c r="J82" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10">
+        <v>17.0</v>
+      </c>
+      <c r="K82" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L82" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M82" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N82" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="O82" s="11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="83" spans="8:8" ht="14.9">
       <c r="A83" s="1">
-        <v>82</v>
+        <v>82.0</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G83" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="H83" s="9" t="s">
+        <v>117</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>90</v>
       </c>
       <c r="J83" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10">
+        <v>17.0</v>
+      </c>
+      <c r="K83" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L83" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M83" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N83" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="O83" s="9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="84" spans="8:8" ht="14.9">
       <c r="A84" s="1">
-        <v>83</v>
+        <v>83.0</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G84" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="H84" s="9" t="s">
+        <v>117</v>
       </c>
       <c r="I84" s="2" t="s">
         <v>90</v>
       </c>
       <c r="J84" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10">
+        <v>17.0</v>
+      </c>
+      <c r="K84" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L84" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M84" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N84" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="O84" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="85" spans="8:8" ht="14.9">
       <c r="A85" s="1">
-        <v>84</v>
+        <v>84.0</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H85" s="9" t="s">
+        <v>117</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>90</v>
       </c>
       <c r="J85" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10">
+        <v>17.0</v>
+      </c>
+      <c r="K85" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L85" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M85" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N85" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="O85" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="86" spans="8:8" ht="14.9">
       <c r="A86" s="1">
-        <v>85</v>
+        <v>85.0</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H86" s="9" t="s">
+        <v>117</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>90</v>
       </c>
       <c r="J86" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10">
+        <v>17.0</v>
+      </c>
+      <c r="K86" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L86" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M86" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N86" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="O86" s="9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="87" spans="8:8" ht="14.9">
       <c r="A87" s="1">
-        <v>86</v>
+        <v>86.0</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H87" s="9" t="s">
+        <v>117</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>90</v>
       </c>
       <c r="J87" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10">
+        <v>18.0</v>
+      </c>
+      <c r="K87" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L87" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M87" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N87" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="O87" s="9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="88" spans="8:8" ht="14.9">
       <c r="A88" s="1">
-        <v>87</v>
+        <v>87.0</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H88" s="9" t="s">
+        <v>117</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>90</v>
       </c>
       <c r="J88" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10">
+        <v>18.0</v>
+      </c>
+      <c r="K88" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L88" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M88" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N88" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="O88" s="9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="89" spans="8:8" ht="14.9">
       <c r="A89" s="1">
-        <v>88</v>
+        <v>88.0</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>90</v>
       </c>
       <c r="J89" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10">
+        <v>18.0</v>
+      </c>
+      <c r="K89" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L89" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M89" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N89" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="O89" s="9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="90" spans="8:8" ht="14.9">
       <c r="A90" s="1">
-        <v>89</v>
+        <v>89.0</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>90</v>
       </c>
       <c r="J90" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10">
+        <v>18.0</v>
+      </c>
+      <c r="K90" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L90" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M90" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N90" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="O90" s="9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="91" spans="8:8" ht="14.9">
       <c r="A91" s="1">
-        <v>90</v>
+        <v>90.0</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="I91" s="2" t="s">
         <v>91</v>
       </c>
       <c r="J91" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10">
+        <v>18.0</v>
+      </c>
+      <c r="K91" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L91" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M91" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N91" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="O91" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="92" spans="8:8" ht="14.9">
       <c r="A92" s="1">
-        <v>91</v>
+        <v>91.0</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>91</v>
       </c>
       <c r="J92" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10">
+        <v>19.0</v>
+      </c>
+      <c r="K92" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L92" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M92" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N92" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="O92" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="P92" s="11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="93" spans="8:8" ht="14.9">
       <c r="A93" s="1">
-        <v>92</v>
+        <v>92.0</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>91</v>
       </c>
       <c r="J93" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10">
+        <v>19.0</v>
+      </c>
+      <c r="K93" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L93" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M93" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N93" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="O93" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="P93" s="9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="94" spans="8:8" ht="14.9">
       <c r="A94" s="1">
-        <v>93</v>
+        <v>93.0</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>91</v>
       </c>
       <c r="J94" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10">
+        <v>19.0</v>
+      </c>
+      <c r="K94" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L94" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M94" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N94" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="O94" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="P94" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="95" spans="8:8" ht="14.9">
       <c r="A95" s="1">
-        <v>94</v>
+        <v>94.0</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>91</v>
       </c>
       <c r="J95" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10">
+        <v>19.0</v>
+      </c>
+      <c r="K95" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L95" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M95" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N95" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="O95" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="P95" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="96" spans="8:8" ht="14.9">
       <c r="A96" s="1">
-        <v>95</v>
+        <v>95.0</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>91</v>
       </c>
       <c r="J96" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10">
+        <v>19.0</v>
+      </c>
+      <c r="K96" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L96" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M96" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N96" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="O96" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="P96" s="9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="97" spans="8:8" ht="14.9">
       <c r="A97" s="1">
-        <v>96</v>
+        <v>96.0</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>91</v>
       </c>
       <c r="J97" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10">
+        <v>20.0</v>
+      </c>
+      <c r="K97" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L97" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M97" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N97" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="O97" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="P97" s="9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="98" spans="8:8" ht="14.9">
       <c r="A98" s="1">
-        <v>97</v>
+        <v>97.0</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>91</v>
       </c>
       <c r="J98" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10">
+        <v>20.0</v>
+      </c>
+      <c r="K98" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L98" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M98" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N98" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="O98" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="P98" s="9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="99" spans="8:8" ht="14.9">
       <c r="A99" s="1">
-        <v>98</v>
+        <v>98.0</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>91</v>
       </c>
       <c r="J99" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10">
+        <v>20.0</v>
+      </c>
+      <c r="K99" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L99" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M99" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N99" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="O99" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="P99" s="9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="100" spans="8:8" ht="14.9">
       <c r="A100" s="1">
-        <v>99</v>
+        <v>99.0</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>91</v>
       </c>
       <c r="J100" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10">
+        <v>20.0</v>
+      </c>
+      <c r="K100" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L100" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M100" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N100" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="O100" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="P100" s="9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="101" spans="8:8" ht="14.9">
       <c r="A101" s="1">
-        <v>100</v>
+        <v>100.0</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>92</v>
       </c>
       <c r="J101" s="1">
-        <v>20</v>
-      </c>
+        <v>20.0</v>
+      </c>
+      <c r="K101" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L101" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M101" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N101" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="O101" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="P101" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="102" spans="8:8">
+      <c r="L102" s="11"/>
+    </row>
+    <row r="103" spans="8:8">
+      <c r="L103" s="11"/>
+    </row>
+    <row r="104" spans="8:8">
+      <c r="L104" s="11"/>
+    </row>
+    <row r="105" spans="8:8">
+      <c r="L105" s="11"/>
+    </row>
+    <row r="106" spans="8:8">
+      <c r="L106" s="11"/>
+    </row>
+    <row r="107" spans="8:8">
+      <c r="L107" s="11"/>
+    </row>
+    <row r="108" spans="8:8">
+      <c r="L108" s="11"/>
+    </row>
+    <row r="109" spans="8:8">
+      <c r="L109" s="11"/>
+    </row>
+    <row r="110" spans="8:8">
+      <c r="L110" s="11"/>
+    </row>
+    <row r="111" spans="8:8">
+      <c r="L111" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="14.25" defaultColWidth="10"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="14.25" defaultColWidth="10"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="14.25" defaultColWidth="10"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>